--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -177,7 +177,7 @@
     <t>MEDICOTECH</t>
   </si>
   <si>
-    <t>medico technique (radio, scanner, ...)</t>
+    <t>Médico technique (radio, scanner, ...)</t>
   </si>
   <si>
     <t>MAG</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -528,7 +528,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -540,7 +542,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -552,7 +556,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -564,7 +570,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -576,7 +584,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -588,7 +598,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -600,7 +612,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
